--- a/data/trans_camb/IP16B06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Provincia-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-27,08</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-14,22</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-27,08%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-14,22%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1829,173 +1829,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>-27,08</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-14,22</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>-78,5; 0,0</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>-60,45; 0,0</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>-27,08%</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-14,22%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>-78,5; 0,0</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>-60,45; 0,0</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A36:A39"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>

--- a/data/trans_camb/IP16B06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Provincia-trans_camb.xlsx
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
